--- a/daily_matches/job_matches_2026-10-12.xlsx
+++ b/daily_matches/job_matches_2026-10-12.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,25 +456,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Algorithmic Trader — Interview Today, Start Tomorrow!</t>
+          <t>Senior Databricks Platform Engineer (Remote US)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Meme House LA, Inc</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, USA USA</t>
+          <t>Reston, VA, USA USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>25.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Copilot, Mistral, Hugging Face, Pinecone, PyTorch, S3</t>
+          <t>AI Engineer, Generative AI, RAG, AWS SageMaker, Synapse, Data Lake, MLflow, FastAPI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -484,67 +484,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d4c02190c8806d0</t>
+          <t>https://www.indeed.com/viewjob?jk=567f4ddfd333af1a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Hub-Remote: DC or Philly Metro)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Element 84</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Alexandria, VA, USA USA</t>
+          <t>Alpharetta, GA, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>21.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Glue, Athena, Redshift, Data Lake, Docker, Kubernetes, CI/CD, Snowflake</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Mistral, Prompt Engineering, Cortex, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf2162b37870f256</t>
+          <t>https://www.indeed.com/viewjob?jk=27a1347e63b333ff</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Azure Ops/AI Engineer (US Remote)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Visibol</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Reston, VA, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, PostgreSQL, MySQL, NoSQL, Python</t>
+          <t>AI Engineer, RAG, AWS SageMaker, Synapse, Data Lake, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,42 +554,532 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cdaf76f16c112ab</t>
+          <t>https://www.indeed.com/viewjob?jk=194ae6ae0e83b1f9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nu Image Medical</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mahwah, NJ, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, MLflow, Docker, CI/CD, GitHub Actions, Git, PySpark</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff02c5e627bf52c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Senior Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kiewit Corporation</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Omaha, NE, USA USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f3210094a7b1a68</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Senior Databricks Data Analyst</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Stitch Consulting Services, Inc.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>USA USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Gemini, Redshift, BigQuery, Git, Snowflake, Databricks, BigQuery, Redshift, PySpark, Tableau</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=287dcd1bbf750e92</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AI Full Stack Engineer - Dallas, TX</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Cystems Logic Inc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Dallas, TX, USA USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Pinecone, S3, FastAPI, PostgreSQL, MongoDB, Cassandra, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34ab6141a1b3831f</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>T prods solutions inc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>El Paso, TX, USA USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, PostgreSQL, MySQL, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aed15eb60f15f6e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AI Engineer in the USA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Andersen</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Remote, USA USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Docker, CI/CD, GitHub Actions, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=30e040163962f6b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sr AI Solutions Specialist - Architecture Foundry</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CME Group</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Chicago, IL, USA USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Gemini, Pinecone, Prompt Engineering, TensorFlow, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=626e5dce758e5ab8</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Snowflake dbt Developer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Victaulic</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>VA, USA USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Cortex, Data Lake, Git, Snowflake, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef7cf14a046fe980</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, USA USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da31ce66bd2bac28</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior AWS Developer (Java Spring Boot) 6454565</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Logic, Inc.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Chicago, IL, USA USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, R, Java</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea60007b0d463606</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Sr Cloud Data and AI Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Chicago, IL, USA USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>11.1</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, AKS, CI/CD, GitHub Actions, Terraform, Git, MySQL, SQL, R</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=90ec722c8443c70b</t>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Cortex, Git, Snowflake, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ebece57643cc8a61</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Empirical Security</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>USA USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, S3, CI/CD, PostgreSQL, MySQL, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=38a9d2b4f085a03c</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Associate Site Reliability Engineer/Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>C3 AI</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Redwood City, CA, USA USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Generative AI, Kubernetes, Terraform, Git, Cassandra, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b511b2cb7189734</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Capability Engineer – Next-Gen Pet Center Technologies</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Mars</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Lewisburg, OH, USA USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, PyTorch, Data Lake, MLflow, Docker, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=63202df230bab42b</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior DevOps and Infrastructure Engineer New</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Smartcat</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>GA, USA USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, CI/CD, Git, Kafka, MongoDB, R, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=661c5630216c22dc</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-10-12.xlsx
+++ b/daily_matches/job_matches_2026-10-12.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,25 +456,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Databricks Platform Engineer (Remote US)</t>
+          <t>Azure Databricks Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>CALLISTOFUSION</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Reston, VA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25.6</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, AWS SageMaker, Synapse, Data Lake, MLflow, FastAPI, Docker, Kubernetes</t>
+          <t>AI Engineer, RAG, Prompt Engineering, S3, Synapse, Data Lake, CI/CD, GitHub Actions, Git, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -484,32 +484,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=567f4ddfd333af1a</t>
+          <t>https://www.indeed.com/viewjob?jk=2ef0def19f3a7249</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>C2 - Data Architect/Data Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.1</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Mistral, Prompt Engineering, Cortex, TensorFlow, PyTorch</t>
+          <t>RAG, BigQuery, Data Lake, CI/CD, Git, Snowflake, Databricks, BigQuery, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -519,32 +519,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27a1347e63b333ff</t>
+          <t>https://www.indeed.com/viewjob?jk=ff331119fd9599f7</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Azure Ops/AI Engineer (US Remote)</t>
+          <t>IT Software Developer, Senior</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Reston, VA, USA USA</t>
+          <t>San Diego, CA, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, AWS SageMaker, Synapse, Data Lake, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+          <t>AI Engineer, Generative AI, RAG, Docker, Kubernetes, CI/CD, Git, Kafka, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,32 +554,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=194ae6ae0e83b1f9</t>
+          <t>https://www.indeed.com/viewjob?jk=1dc1d6539719ae41</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>NextPathAI</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Tampa, FL, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, MLflow, Docker, CI/CD, GitHub Actions, Git, PySpark</t>
+          <t>Data Scientist, RAG, TensorFlow, Keras, Azure ML, Data Lake, CI/CD, Git, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,32 +589,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff02c5e627bf52c0</t>
+          <t>https://www.indeed.com/viewjob?jk=a90bda5dfb22d7d1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Omaha, NE, USA USA</t>
+          <t>Salt Lake City, UT, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>Gemini, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,32 +624,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f3210094a7b1a68</t>
+          <t>https://www.indeed.com/viewjob?jk=5363b16bc4c31f5a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Databricks Data Analyst</t>
+          <t>Associate AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Stitch Consulting Services, Inc.</t>
+          <t>Trinzic</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Sioux Falls, SD, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gemini, Redshift, BigQuery, Git, Snowflake, Databricks, BigQuery, Redshift, PySpark, Tableau</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, Docker, Kubernetes, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,24 +659,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=287dcd1bbf750e92</t>
+          <t>https://www.indeed.com/viewjob?jk=075accddbedd75ac</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Full Stack Engineer - Dallas, TX</t>
+          <t>GenAI Engineer (Full Stack or Backend Engineer)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cystems Logic Inc</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -684,7 +684,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Pinecone, S3, FastAPI, PostgreSQL, MongoDB, Cassandra, Python, SQL</t>
+          <t>AI Engineer, Generative AI, RAG, FastAPI, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,24 +694,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ab6141a1b3831f</t>
+          <t>https://www.indeed.com/viewjob?jk=0b4b37b0490789e6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Sr AI/ML Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>T prods solutions inc</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>El Paso, TX, USA USA</t>
+          <t>Minnetonka, MN, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -719,7 +719,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, PostgreSQL, MySQL, NoSQL, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, Copilot, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, MySQL, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,19 +729,19 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aed15eb60f15f6e3</t>
+          <t>https://www.indeed.com/viewjob?jk=37fd53bc295db27f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Engineer in the USA</t>
+          <t>AI Engineering – New College Graduate 2027</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Andersen</t>
+          <t>Bitdeer Technologies Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -750,11 +750,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Docker, CI/CD, GitHub Actions, Git, Python, R</t>
+          <t>AI Engineer, RAG, Docker, Kubernetes, Terraform, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,32 +764,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30e040163962f6b4</t>
+          <t>https://www.indeed.com/viewjob?jk=8790c163f75122be</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr AI Solutions Specialist - Architecture Foundry</t>
+          <t>Artificial Intelligence Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CME Group</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Des Moines, IA, USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Gemini, Pinecone, Prompt Engineering, TensorFlow, Python, R, Java</t>
+          <t>AI Engineer, Generative AI, RAG, BigQuery, Dataflow, Git, BigQuery, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,24 +799,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=626e5dce758e5ab8</t>
+          <t>https://www.indeed.com/viewjob?jk=a42274c303c01142</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Snowflake dbt Developer</t>
+          <t>Sr. Data Analyst, Customer Analytics (Insurance)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Victaulic</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>VA, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -824,7 +824,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Cortex, Data Lake, Git, Snowflake, Power BI, Python, SQL, R</t>
+          <t>Generative AI, Prompt Engineering, BigQuery, Snowflake, BigQuery, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,24 +834,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef7cf14a046fe980</t>
+          <t>https://www.indeed.com/viewjob?jk=695ba904f3279d5d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Trinzic</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, USA USA</t>
+          <t>Sioux Falls, SD, USA USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -859,7 +859,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, R, Java, Scala</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, GitHub Actions, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -869,32 +869,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da31ce66bd2bac28</t>
+          <t>https://www.indeed.com/viewjob?jk=6fe15f3fd01de120</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior AWS Developer (Java Spring Boot) 6454565</t>
+          <t>AI Workflow Engineer and Developer (Remote)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>Augusto Digital</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, R, Java</t>
+          <t>RAG, Copilot, Prompt Engineering, Docker, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,24 +904,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea60007b0d463606</t>
+          <t>https://www.indeed.com/viewjob?jk=c32f9559662b29de</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr Cloud Data and AI Engineer</t>
+          <t>AI Engineer- Open Source LLMs</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>NextPathAI</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Tampa, FL, USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -929,7 +929,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Cortex, Git, Snowflake, Python, SQL, R, Scala</t>
+          <t>AI Engineer, RAG, LLaMA, Mistral, TensorFlow, PyTorch, Python, R, Java, C++</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -939,24 +939,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebece57643cc8a61</t>
+          <t>https://www.indeed.com/viewjob?jk=9d263ba7c3d79def</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Engineer / Senior Engineer – AI Model Enablement &amp; Software Tools</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Empirical Security</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>San Diego, CA, USA USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -964,7 +964,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, PostgreSQL, MySQL, Python, SQL, R, Scala, Optimization</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, Hugging Face, PyTorch, Git, Python, R, C++, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -974,24 +974,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38a9d2b4f085a03c</t>
+          <t>https://www.indeed.com/viewjob?jk=9fc8c2c9d4929650</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Associate Site Reliability Engineer/Site Reliability Engineer</t>
+          <t>Senior Associate-Applied Artificial Intelligence / Machine Learning</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>C3 AI</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Redwood City, CA, USA USA</t>
+          <t>Palo Alto, CA, USA USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -999,7 +999,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Generative AI, Kubernetes, Terraform, Git, Cassandra, NoSQL, Python, SQL, R, Scala</t>
+          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, PyTorch, scikit-learn, Python, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1009,24 +1009,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b511b2cb7189734</t>
+          <t>https://www.indeed.com/viewjob?jk=3373d021dc04986c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capability Engineer – Next-Gen Pet Center Technologies</t>
+          <t>Intermediate Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Gordon Food Service</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lewisburg, OH, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Copilot, PyTorch, Data Lake, MLflow, Docker, Git, Python, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1044,24 +1044,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63202df230bab42b</t>
+          <t>https://www.indeed.com/viewjob?jk=60ca7e7cf50a8d3e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior DevOps and Infrastructure Engineer New</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Smartcat</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GA, USA USA</t>
+          <t>Eden Prairie, MN, USA USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, CI/CD, Git, Kafka, MongoDB, R, Scala</t>
+          <t>Generative AI, RAG, CI/CD, Databricks, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1079,7 +1079,147 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=661c5630216c22dc</t>
+          <t>https://www.indeed.com/viewjob?jk=3cbb05a21e338618</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>NextPathAI</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Tampa, FL, USA USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, scikit-learn, Matplotlib, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e1daeaceb2d78ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>LLM Serving Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>San Diego, CA, USA USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, PyTorch, Keras, Git, Python, R, C++, Optimization</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=babb4cd0ce60fe9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>EnergyHub</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>New York, NY, USA USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, PostgreSQL, MongoDB, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7c5ea12d8497425d</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Associate Data Scientist</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Westport Properties, Inc.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Remote, USA USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Git, Snowflake, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d6703ec0ae4b1acf</t>
         </is>
       </c>
     </row>
